--- a/survey_templates/020_product_customer_feedback_form--survey_templates.xlsx
+++ b/survey_templates/020_product_customer_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_id':_1,_'value':_'very_likely_to_recommend'}</t>
+          <t>very_likely_to_recommend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_id': 1, 'value': 'Very Likely to Recommend'}</t>
+          <t>Very Likely to Recommend</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_id':_2,_'value':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_id': 2, 'value': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_id':_3,_'value':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_id': 3, 'value': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_id':_4,_'value':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_id': 4, 'value': 'Not At All Likely'}</t>
+          <t>Not At All Likely</t>
         </is>
       </c>
     </row>
